--- a/testdata/BidDetailsData.xlsx.xlsx
+++ b/testdata/BidDetailsData.xlsx.xlsx
@@ -7,12 +7,12 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="15030" windowHeight="3630"/>
   </bookViews>
   <sheets>
-    <sheet name="Catalog_data" sheetId="1" r:id="rId1"/>
+    <sheet name="BidData" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>CatalogType</t>
   </si>
@@ -55,13 +55,28 @@
   </si>
   <si>
     <t>EmdAmount-DeductedInRealTime</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Pass@8319061655</t>
+  </si>
+  <si>
+    <t>Pass@1234</t>
+  </si>
+  <si>
+    <t>Difference-In-Freepool-AfterBidding</t>
+  </si>
+  <si>
+    <t>Difference-In-Blockedpool-AfterBidding</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,6 +98,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -101,10 +124,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -121,8 +145,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -420,20 +448,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AK4"/>
+  <dimension ref="A1:AL4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="13.42578125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="3" customWidth="1"/>
-    <col min="6" max="7" width="12" style="3" customWidth="1"/>
-    <col min="8" max="10" width="10.28515625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="3" width="13.42578125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" style="3" customWidth="1"/>
+    <col min="7" max="8" width="12" style="3" customWidth="1"/>
+    <col min="9" max="11" width="10.28515625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="10.85546875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" ht="90" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -441,32 +470,38 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
+      <c r="L1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
@@ -479,30 +514,56 @@
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="3">
         <v>61000105</v>
       </c>
+      <c r="C2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1828003460.03</v>
+      </c>
       <c r="E2" s="3">
+        <v>13084425.689999999</v>
+      </c>
+      <c r="F2" s="3">
+        <v>117</v>
+      </c>
+      <c r="G2" s="3">
         <v>100</v>
       </c>
-      <c r="F2" s="3">
-        <v>100</v>
-      </c>
-      <c r="O2" s="5"/>
+      <c r="H2" s="3">
+        <v>58914.18</v>
+      </c>
+      <c r="I2" s="3">
+        <v>1828002956.53</v>
+      </c>
+      <c r="J2" s="3">
+        <v>13084929.189999999</v>
+      </c>
+      <c r="L2" s="3">
+        <f>D2-I2</f>
+        <v>503.5</v>
+      </c>
+      <c r="M2" s="3">
+        <f>J2-E2</f>
+        <v>503.5</v>
+      </c>
       <c r="P2" s="5"/>
-      <c r="Q2" s="4"/>
+      <c r="Q2" s="5"/>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
-      <c r="V2" s="5"/>
+      <c r="V2" s="4"/>
       <c r="W2" s="5"/>
-      <c r="X2" s="4"/>
+      <c r="X2" s="5"/>
       <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
       <c r="AA2" s="4"/>
@@ -516,52 +577,109 @@
       <c r="AI2" s="4"/>
       <c r="AJ2" s="4"/>
       <c r="AK2" s="4"/>
+      <c r="AL2" s="4"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="3">
         <v>61000106</v>
       </c>
+      <c r="C3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3">
+        <v>168466040.02000001</v>
+      </c>
       <c r="E3" s="3">
-        <v>101</v>
+        <v>10011197.880000001</v>
       </c>
       <c r="F3" s="3">
+        <v>118</v>
+      </c>
+      <c r="G3" s="3">
         <v>100</v>
       </c>
+      <c r="H3" s="3">
+        <v>58914.18</v>
+      </c>
+      <c r="I3" s="3">
+        <v>168406622.22</v>
+      </c>
+      <c r="J3" s="3">
+        <v>10070615.68</v>
+      </c>
+      <c r="L3" s="3">
+        <f>D3-I3</f>
+        <v>59417.800000011921</v>
+      </c>
+      <c r="M3" s="3">
+        <f>J3-E3</f>
+        <v>59417.799999998882</v>
+      </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="3">
         <v>61000101</v>
       </c>
+      <c r="C4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1033142390.34</v>
+      </c>
       <c r="E4" s="3">
-        <v>102</v>
+        <v>9016203.7200000007</v>
       </c>
       <c r="F4" s="3">
+        <v>119</v>
+      </c>
+      <c r="G4" s="3">
         <v>100</v>
+      </c>
+      <c r="H4" s="3">
+        <v>58914.18</v>
+      </c>
+      <c r="I4" s="3">
+        <v>1033082469.04</v>
+      </c>
+      <c r="J4" s="3">
+        <v>9076125.0199999996</v>
+      </c>
+      <c r="L4" s="3">
+        <f>D4-I4</f>
+        <v>59921.300000071526</v>
+      </c>
+      <c r="M4" s="3">
+        <f>J4-E4</f>
+        <v>59921.299999998882</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AB2">
       <formula1>"Y,N,CLIENT SAP,Cl SAP + Y,GST"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA2">
       <formula1>"Y,N,P"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="U2">
+    <dataValidation type="list" allowBlank="1" sqref="V2">
       <formula1>"Nafed Stage 1,Nafed Stage 2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="T2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="U2">
       <formula1>"INR,USD,AED"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1"/>
+    <hyperlink ref="C4" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
@@ -569,19 +687,19 @@
           <x14:formula1>
             <xm:f>'C:\Users\Admin\Downloads\[techformat_154878_2026-02-23_13.02.24.xlsx]hidden3'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>Y2</xm:sqref>
+          <xm:sqref>Z2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'C:\Users\Admin\Downloads\[techformat_154878_2026-02-23_13.02.24.xlsx]hidden'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>X2</xm:sqref>
+          <xm:sqref>Y2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'C:\Users\Admin\Downloads\[techformat_154878_2026-02-23_13.02.24.xlsx]hidden2'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>S2</xm:sqref>
+          <xm:sqref>T2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/testdata/BidDetailsData.xlsx.xlsx
+++ b/testdata/BidDetailsData.xlsx.xlsx
@@ -12,9 +12,9 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" fullCalcOnLoad="true"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -76,6 +76,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -451,15 +452,15 @@
   <dimension ref="A1:AL4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="13.42578125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" style="3" customWidth="1"/>
-    <col min="7" max="8" width="12" style="3" customWidth="1"/>
-    <col min="9" max="11" width="10.28515625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="11.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="3" customWidth="true" style="3" width="13.42578125"/>
+    <col min="4" max="4" customWidth="true" style="3" width="14.42578125"/>
+    <col min="5" max="5" customWidth="true" style="3" width="13.42578125"/>
+    <col min="6" max="6" customWidth="true" style="3" width="11.5703125"/>
+    <col min="7" max="8" customWidth="true" style="3" width="12.0"/>
+    <col min="9" max="11" customWidth="true" style="3" width="10.28515625"/>
+    <col min="12" max="12" customWidth="true" style="3" width="10.85546875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="3" width="11.28515625"/>
+    <col min="14" max="16384" style="3" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="90" x14ac:dyDescent="0.25">
@@ -526,34 +527,34 @@
       <c r="C2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="3">
-        <v>1828003460.03</v>
-      </c>
-      <c r="E2" s="3">
-        <v>13084425.689999999</v>
+      <c r="D2" s="3" t="n">
+        <v>1.82801076138E9</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>1.307712434E7</v>
       </c>
       <c r="F2" s="3">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G2" s="3">
         <v>100</v>
       </c>
-      <c r="H2" s="3">
-        <v>58914.18</v>
-      </c>
-      <c r="I2" s="3">
-        <v>1828002956.53</v>
-      </c>
-      <c r="J2" s="3">
-        <v>13084929.189999999</v>
+      <c r="H2" s="3" t="n">
+        <v>60424.8</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>1.82795033658E9</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>1.313754914E7</v>
       </c>
       <c r="L2" s="3">
         <f>D2-I2</f>
-        <v>503.5</v>
+        <v>58914.200000047684</v>
       </c>
       <c r="M2" s="3">
         <f>J2-E2</f>
-        <v>503.5</v>
+        <v>58914.199999999255</v>
       </c>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
@@ -589,34 +590,34 @@
       <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3">
-        <v>168466040.02000001</v>
-      </c>
-      <c r="E3" s="3">
-        <v>10011197.880000001</v>
+      <c r="D3" s="3" t="n">
+        <v>1.6846604002E8</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1.001119788E7</v>
       </c>
       <c r="F3" s="3">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G3" s="3">
         <v>100</v>
       </c>
-      <c r="H3" s="3">
-        <v>58914.18</v>
-      </c>
-      <c r="I3" s="3">
-        <v>168406622.22</v>
-      </c>
-      <c r="J3" s="3">
-        <v>10070615.68</v>
+      <c r="H3" s="3" t="n">
+        <v>60928.34</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>1.6840511172E8</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>1.007212618E7</v>
       </c>
       <c r="L3" s="3">
         <f>D3-I3</f>
-        <v>59417.800000011921</v>
+        <v>59417.700000017881</v>
       </c>
       <c r="M3" s="3">
         <f>J3-E3</f>
-        <v>59417.799999998882</v>
+        <v>59417.699999999255</v>
       </c>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.25">
@@ -629,34 +630,34 @@
       <c r="C4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="3">
-        <v>1033142390.34</v>
-      </c>
-      <c r="E4" s="3">
-        <v>9016203.7200000007</v>
+      <c r="D4" s="3" t="n">
+        <v>1.03306508678E9</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>9093507.28</v>
       </c>
       <c r="F4" s="3">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G4" s="3">
         <v>100</v>
       </c>
-      <c r="H4" s="3">
-        <v>58914.18</v>
-      </c>
-      <c r="I4" s="3">
-        <v>1033082469.04</v>
-      </c>
-      <c r="J4" s="3">
-        <v>9076125.0199999996</v>
+      <c r="H4" s="3" t="n">
+        <v>61431.88</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>1.03300365488E9</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>9154939.18</v>
       </c>
       <c r="L4" s="3">
         <f>D4-I4</f>
-        <v>59921.300000071526</v>
+        <v>59921.299999952316</v>
       </c>
       <c r="M4" s="3">
         <f>J4-E4</f>
-        <v>59921.299999998882</v>
+        <v>59921.300000000745</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/BidDetailsData.xlsx.xlsx
+++ b/testdata/BidDetailsData.xlsx.xlsx
@@ -534,27 +534,27 @@
         <v>1.307712434E7</v>
       </c>
       <c r="F2" s="3">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G2" s="3">
         <v>100</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>60424.8</v>
+        <v>63446.04</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>1.82795033658E9</v>
+        <v>1.82794731538E9</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.313754914E7</v>
+        <v>1.314057034E7</v>
       </c>
       <c r="L2" s="3">
         <f>D2-I2</f>
-        <v>58914.200000047684</v>
+        <v>61935.400000095367</v>
       </c>
       <c r="M2" s="3">
         <f>J2-E2</f>
-        <v>58914.199999999255</v>
+        <v>61935.400000000373</v>
       </c>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
@@ -597,27 +597,27 @@
         <v>1.001119788E7</v>
       </c>
       <c r="F3" s="3">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G3" s="3">
         <v>100</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>60928.34</v>
+        <v>63949.58</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1.6840511172E8</v>
+        <v>1.6840209042E8</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.007212618E7</v>
+        <v>1.007514748E7</v>
       </c>
       <c r="L3" s="3">
         <f>D3-I3</f>
-        <v>59417.700000017881</v>
+        <v>62439</v>
       </c>
       <c r="M3" s="3">
         <f>J3-E3</f>
-        <v>59417.699999999255</v>
+        <v>62439</v>
       </c>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.25">
@@ -637,27 +637,27 @@
         <v>9093507.28</v>
       </c>
       <c r="F4" s="3">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G4" s="3">
         <v>100</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>61431.88</v>
+        <v>64453.12</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1.03300365488E9</v>
+        <v>1.03300063368E9</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>9154939.18</v>
+        <v>9157960.38</v>
       </c>
       <c r="L4" s="3">
         <f>D4-I4</f>
-        <v>59921.299999952316</v>
+        <v>62942.5</v>
       </c>
       <c r="M4" s="3">
         <f>J4-E4</f>
-        <v>59921.300000000745</v>
+        <v>62942.5</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/BidDetailsData.xlsx.xlsx
+++ b/testdata/BidDetailsData.xlsx.xlsx
@@ -534,27 +534,27 @@
         <v>1.307712434E7</v>
       </c>
       <c r="F2" s="3">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="G2" s="3">
         <v>100</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>63446.04</v>
+        <v>50354.0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>1.82794731538E9</v>
+        <v>1.82796040738E9</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.314057034E7</v>
+        <v>1.312747834E7</v>
       </c>
       <c r="L2" s="3">
         <f>D2-I2</f>
-        <v>61935.400000095367</v>
+        <v>63446</v>
       </c>
       <c r="M2" s="3">
         <f>J2-E2</f>
-        <v>61935.400000000373</v>
+        <v>63446</v>
       </c>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
@@ -597,27 +597,27 @@
         <v>1.001119788E7</v>
       </c>
       <c r="F3" s="3">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="G3" s="3">
         <v>100</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>63949.58</v>
+        <v>50857.54</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1.6840209042E8</v>
+        <v>1.6841518252E8</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.007514748E7</v>
+        <v>1.006205538E7</v>
       </c>
       <c r="L3" s="3">
         <f>D3-I3</f>
-        <v>62439</v>
+        <v>63949.600000023842</v>
       </c>
       <c r="M3" s="3">
         <f>J3-E3</f>
-        <v>62439</v>
+        <v>63949.599999999627</v>
       </c>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.25">
@@ -631,33 +631,33 @@
         <v>13</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.03306508678E9</v>
+        <v>1.03299358412E9</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>9093507.28</v>
+        <v>9157960.38</v>
       </c>
       <c r="F4" s="3">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="G4" s="3">
         <v>100</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>64453.12</v>
+        <v>51361.08</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1.03300063368E9</v>
+        <v>1.03294222302E9</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>9157960.38</v>
+        <v>9209321.48</v>
       </c>
       <c r="L4" s="3">
         <f>D4-I4</f>
-        <v>62942.5</v>
+        <v>64453.100000023842</v>
       </c>
       <c r="M4" s="3">
         <f>J4-E4</f>
-        <v>62942.5</v>
+        <v>64453.10000000149</v>
       </c>
     </row>
   </sheetData>
